--- a/results/Int All Data 0.4/Linea_fi_all.xlsx
+++ b/results/Int All Data 0.4/Linea_fi_all.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0010582010582010249 +/- 0.0002160043864888096</t>
+          <t>0.0010141093474426489 +/- 0.00020205360207035695</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0002645502645502562 +/- 0.0002924713219008197</t>
+          <t>0.00030864197530863227 +/- 0.00028232470182683626</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.001528776978417301 +/- 0.0018341796811484898</t>
+          <t>0.0015287769784173122 +/- 0.001720425042240024</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -2346,74 +2346,74 @@
       </c>
       <c r="BW3" t="inlineStr">
         <is>
+          <t>0.0003147482014388858 +/- 0.0003511802911828517</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.0020233812949640773 +/- 0.001856638742991259</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.006654676258992853 +/- 0.001079136690647478</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.006654676258992853 +/- 0.001079136690647478</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.006070143884892109 +/- 0.0016973548640446731</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>0.08142985611510795 +/- 0.004058984342116914</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.0038219424460431916 +/- 0.0025055093013947928</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>-0.0005395683453237043 +/- 0.0025179856115108046</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>-0.00206834532374095 +/- 0.0021299854824329127</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>0.0006744604316546998 +/- 0.001193877522243846</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>0.5616007194244604 +/- 0.005247515993127759</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>0.013084532374100755 +/- 0.0028892668752549173</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>0.2571043165467626 +/- 0.004221832587879682</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
           <t>0.00022482014388491844 +/- 0.0003625115894019144</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.0020233812949640773 +/- 0.001856638742991259</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.006654676258992853 +/- 0.001079136690647478</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.006654676258992853 +/- 0.001079136690647478</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.006070143884892109 +/- 0.0016973548640446731</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.08147482014388494 +/- 0.004105292162055164</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.003866906474820175 +/- 0.002456205087004972</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>-0.0005395683453237043 +/- 0.0025179856115108046</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>-0.00206834532374095 +/- 0.0021299854824329127</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.0005845323741007324 +/- 0.0012239799989942491</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>0.5616007194244604 +/- 0.005247515993127759</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>0.013084532374100755 +/- 0.0028892668752549173</t>
-        </is>
-      </c>
-      <c r="CI3" t="inlineStr">
-        <is>
-          <t>0.2571043165467626 +/- 0.004221832587879682</t>
-        </is>
-      </c>
-      <c r="CJ3" t="inlineStr">
-        <is>
-          <t>0.0003147482014388858 +/- 0.0003511802911828517</t>
-        </is>
-      </c>
       <c r="CK3" t="inlineStr">
         <is>
           <t>0.0027428057553957274 +/- 0.0017350522825157317</t>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>0.05867805755395687 +/- 0.004942976485520764</t>
+          <t>0.05863309352517989 +/- 0.004946860625710461</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>3.3306690738754695e-17 +/- 0.00034828986926325475</t>
+          <t>-4.4964028776950385e-05 +/- 0.000314748201438843</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.0020206766917293174 +/- 0.0007295194876062125</t>
+          <t>-0.0019736842105263163 +/- 0.0008084892168273108</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>0.011372180451127811 +/- 0.0021307864753298314</t>
+          <t>0.011419172932330812 +/- 0.0020915613801003835</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>0.019455087271179273 +/- 0.0038552308552297775</t>
+          <t>0.019497658578118394 +/- 0.003787650305582844</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.00174542358450408 +/- 0.0004016169064306795</t>
+          <t>0.001787994891443201 +/- 0.00041711191873702457</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>0.02320136228182208 +/- 0.005674134016753716</t>
+          <t>0.0232439335887612 +/- 0.005629079498021481</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="EB7" t="inlineStr">
         <is>
-          <t>0.02320136228182208 +/- 0.005674134016753716</t>
+          <t>0.02324393358876121 +/- 0.005651571485832626</t>
         </is>
       </c>
       <c r="EC7" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>-0.02573149741824443 +/- 0.0011513845232581383</t>
+          <t>-0.025774526678141164 +/- 0.0011457424230373724</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.007745266781411364 +/- 0.0006938259680119094</t>
+          <t>-0.0077022375215146325 +/- 0.0007563853627903066</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>0.03844483058210255 +/- 0.0052426386534241785</t>
+          <t>0.038488271068636004 +/- 0.00529261317481078</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>-0.0065795613625758255 +/- 0.001525691341509268</t>
+          <t>-0.006532897806812876 +/- 0.0015192553052822864</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-0.002405498281786933 +/- 0.0015511572238202512</t>
+          <t>-0.002319587628865971 +/- 0.00147806276066024</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
